--- a/GP2/Versuch_O4/Versuchsmitschriften_O4.xlsx
+++ b/GP2/Versuch_O4/Versuchsmitschriften_O4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_O4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837200CC-E241-AE4A-A195-7DB20BAA2997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E1E8B4-282A-FD48-8951-090836AA49E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{6F72763A-2E3C-0A4F-8440-476F0F86E04E}"/>
   </bookViews>
